--- a/自考本科/个人学习笔记/Byvm815/毕业时间预测表.xlsx
+++ b/自考本科/个人学习笔记/Byvm815/毕业时间预测表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>2026年</t>
   </si>
@@ -161,12 +161,15 @@
 最晚自考本科报考毕业论文时间</t>
     </r>
   </si>
+  <si>
+    <t>注：承办主考学校以深圳大学做预测</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -187,6 +190,16 @@
     <font>
       <sz val="8.000000"/>
       <color theme="0" tint="-0.499984740745262"/>
+      <name val="等距更纱黑体 SC Light"/>
+    </font>
+    <font>
+      <sz val="16.000000"/>
+      <color rgb="FFD8D8D8"/>
+      <name val="等距更纱黑体 SC Light"/>
+    </font>
+    <font>
+      <sz val="16.000000"/>
+      <color theme="1" tint="0"/>
       <name val="等距更纱黑体 SC Light"/>
     </font>
   </fonts>
@@ -278,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -316,6 +329,10 @@
     </xf>
     <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1127,8 +1144,20 @@
       </c>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" ht="14.25">
-      <c r="D14" s="1"/>
+    <row r="14" s="14" customFormat="1" ht="21.75">
+      <c r="A14" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
     </row>
     <row r="15" ht="14.25">
       <c r="D15" s="1"/>
@@ -1164,11 +1193,12 @@
       <c r="D25" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A14:K14"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/自考本科/个人学习笔记/Byvm815/毕业时间预测表.xlsx
+++ b/自考本科/个人学习笔记/Byvm815/毕业时间预测表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>2026年</t>
   </si>
@@ -33,6 +33,10 @@
     <t>一月</t>
   </si>
   <si>
+    <t xml:space="preserve">自考本科笔试补考机会
+毕业论文重写机会</t>
+  </si>
+  <si>
     <t>二月</t>
   </si>
   <si>
@@ -48,18 +52,73 @@
     <t>自考本科首次考试</t>
   </si>
   <si>
-    <t xml:space="preserve">自考本科通过全部笔试课程
-（一次过）</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">自考本科通过全部笔试课程
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>（一次过）</t>
+    </r>
+  </si>
+  <si>
+    <t>自考本科笔试补考机会</t>
   </si>
   <si>
     <t>五月</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">自考本科通过全部实践考试
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>（一次过）</t>
+    </r>
+  </si>
+  <si>
+    <t>自考本科实践补考机会</t>
+  </si>
+  <si>
     <t>六月</t>
   </si>
   <si>
-    <t xml:space="preserve">自考本科完成毕业论文
-达到毕业要求</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">达到毕业要求
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>（无法申请毕业，专科信息未录入学信网）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -98,7 +157,23 @@
     <t>八月</t>
   </si>
   <si>
-    <t>自考本科通过全部实践考试</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">自考本科报考毕业论文
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>（需要笔试通过9门）</t>
+    </r>
   </si>
   <si>
     <t>九月</t>
@@ -110,7 +185,8 @@
     <t>十月</t>
   </si>
   <si>
-    <t>自考本科笔试补考机会</t>
+    <t xml:space="preserve">自考本科笔试补考机会
+自考本科实践补考机会</t>
   </si>
   <si>
     <r>
@@ -125,10 +201,10 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="等距更纱黑体 SC Light"/>
-      </rPr>
-      <t>（可以报名考研了）</t>
+        <color rgb="FFA5A5A5"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>（可以报名考研了）（由于专科毕业的时间错位，无法在2027年考研）</t>
     </r>
   </si>
   <si>
@@ -138,8 +214,23 @@
     <t>十二月</t>
   </si>
   <si>
-    <t xml:space="preserve">自考本科报考毕业论文
-（需要笔试实践全部通过）</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">自考本科完成毕业论文
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>（一次过）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -162,7 +253,7 @@
     </r>
   </si>
   <si>
-    <t>注：承办主考学校以深圳大学做预测</t>
+    <t>注：承办主考学校以华南理工大学做预测</t>
   </si>
 </sst>
 </file>
@@ -882,7 +973,9 @@
       <c r="G2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="6"/>
+      <c r="H2" s="8" t="s">
+        <v>5</v>
+      </c>
       <c r="I2" s="7"/>
       <c r="J2" s="5" t="s">
         <v>4</v>
@@ -891,262 +984,268 @@
     </row>
     <row r="3" ht="40.100000000000001" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="7"/>
       <c r="G3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="7"/>
       <c r="J3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" ht="40.100000000000001" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="7"/>
       <c r="G4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="7"/>
       <c r="J4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="6"/>
     </row>
     <row r="5" ht="40.100000000000001" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="6"/>
+        <v>9</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="I5" s="7"/>
       <c r="J5" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" ht="40.100000000000001" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="7"/>
       <c r="D6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>14</v>
+      </c>
       <c r="F6" s="7"/>
       <c r="G6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="I6" s="7"/>
       <c r="J6" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K6" s="6"/>
     </row>
     <row r="7" ht="40.100000000000001" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="7"/>
       <c r="D7" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
       <c r="G7" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" ht="40.100000000000001" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="7"/>
       <c r="D8" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
       <c r="G8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K8" s="6"/>
     </row>
     <row r="9" ht="40.100000000000001" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="7"/>
       <c r="J9" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K9" s="6"/>
     </row>
     <row r="10" ht="40.100000000000001" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
       <c r="D10" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="7"/>
       <c r="G10" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="7"/>
       <c r="J10" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="40.100000000000001" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
       <c r="D11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K11" s="8"/>
     </row>
     <row r="12" ht="40.100000000000001" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
       <c r="D12" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
       <c r="G12" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="7"/>
       <c r="J12" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K12" s="6"/>
     </row>
     <row r="13" ht="40.100000000000001" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="7"/>
       <c r="D13" s="11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K13" s="12"/>
     </row>
     <row r="14" s="14" customFormat="1" ht="21.75">
       <c r="A14" s="15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
